--- a/Daily_Report/Top 7 broker List with its Turnover 2024-10-20.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-10-20.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="264">
   <si>
     <t>Date: 2024-10-20</t>
   </si>
@@ -62,106 +62,106 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
-    <t>Sumeru Securities Pvt.Limited</t>
+    <t>Bhrikuti Stock Broking Co. Pvt. Ltd.</t>
   </si>
   <si>
     <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
-    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
+    <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
+    <t>34</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>45</t>
   </si>
   <si>
-    <t>39</t>
+    <t>55</t>
   </si>
   <si>
     <t>57</t>
   </si>
   <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>998,441,354.17</t>
-  </si>
-  <si>
-    <t>570,938,644.9</t>
-  </si>
-  <si>
-    <t>553,125,065.28</t>
-  </si>
-  <si>
-    <t>548,595,368.36</t>
-  </si>
-  <si>
-    <t>527,650,410.92</t>
-  </si>
-  <si>
-    <t>515,305,841.6</t>
-  </si>
-  <si>
-    <t>458,360,639.25</t>
-  </si>
-  <si>
-    <t>647,430,813.9</t>
-  </si>
-  <si>
-    <t>260,747,144.73</t>
-  </si>
-  <si>
-    <t>263,615,486.1</t>
-  </si>
-  <si>
-    <t>282,765,225.2</t>
-  </si>
-  <si>
-    <t>129,275,334.94</t>
-  </si>
-  <si>
-    <t>254,532,713.8</t>
-  </si>
-  <si>
-    <t>206,204,485.7</t>
-  </si>
-  <si>
-    <t>351,010,540.27</t>
-  </si>
-  <si>
-    <t>310,191,500.17</t>
-  </si>
-  <si>
-    <t>289,509,579.18</t>
-  </si>
-  <si>
-    <t>265,830,143.16</t>
-  </si>
-  <si>
-    <t>398,375,075.98</t>
-  </si>
-  <si>
-    <t>260,773,127.8</t>
-  </si>
-  <si>
-    <t>252,156,153.55</t>
+    <t>49</t>
+  </si>
+  <si>
+    <t>902,723,840.97</t>
+  </si>
+  <si>
+    <t>642,584,331.68</t>
+  </si>
+  <si>
+    <t>601,556,918.0</t>
+  </si>
+  <si>
+    <t>599,785,104.36</t>
+  </si>
+  <si>
+    <t>545,058,313.37</t>
+  </si>
+  <si>
+    <t>527,328,997.0</t>
+  </si>
+  <si>
+    <t>471,556,260.04</t>
+  </si>
+  <si>
+    <t>526,039,583.4</t>
+  </si>
+  <si>
+    <t>318,130,976.2</t>
+  </si>
+  <si>
+    <t>280,807,721.89</t>
+  </si>
+  <si>
+    <t>271,933,329.7</t>
+  </si>
+  <si>
+    <t>310,956,549.3</t>
+  </si>
+  <si>
+    <t>241,938,508.9</t>
+  </si>
+  <si>
+    <t>189,842,847.94</t>
+  </si>
+  <si>
+    <t>376,684,257.57</t>
+  </si>
+  <si>
+    <t>324,453,355.48</t>
+  </si>
+  <si>
+    <t>320,749,196.11</t>
+  </si>
+  <si>
+    <t>327,851,774.66</t>
+  </si>
+  <si>
+    <t>234,101,764.07</t>
+  </si>
+  <si>
+    <t>285,390,488.1</t>
+  </si>
+  <si>
+    <t>281,713,412.1</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,190 +182,178 @@
     <t>NGPL</t>
   </si>
   <si>
-    <t>96,780,852.5</t>
+    <t>106,308,397.5</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>44,169,640.2</t>
+  </si>
+  <si>
+    <t>HIDCLP</t>
+  </si>
+  <si>
+    <t>19,150,400.5</t>
   </si>
   <si>
     <t>GFCL</t>
   </si>
   <si>
-    <t>77,755,638.5</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>76,915,693.4</t>
+    <t>18,870,113.5</t>
+  </si>
+  <si>
+    <t>USHL</t>
+  </si>
+  <si>
+    <t>16,860,783.0</t>
+  </si>
+  <si>
+    <t>25,281,327.1</t>
+  </si>
+  <si>
+    <t>PRVU</t>
+  </si>
+  <si>
+    <t>17,426,051.0</t>
+  </si>
+  <si>
+    <t>15,586,804.7</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>8,742,504.1</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>8,697,550.6</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>13,948,728.0</t>
+  </si>
+  <si>
+    <t>13,508,985.9</t>
+  </si>
+  <si>
+    <t>PROFL</t>
+  </si>
+  <si>
+    <t>11,076,579.4</t>
+  </si>
+  <si>
+    <t>9,292,626.8</t>
+  </si>
+  <si>
+    <t>GBBL</t>
+  </si>
+  <si>
+    <t>8,955,879.0</t>
+  </si>
+  <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>23,471,289.2</t>
+  </si>
+  <si>
+    <t>13,375,682.5</t>
+  </si>
+  <si>
+    <t>12,973,795.7</t>
+  </si>
+  <si>
+    <t>PFL</t>
+  </si>
+  <si>
+    <t>5,746,055.8</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>5,519,446.0</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>175,667,603.2</t>
+  </si>
+  <si>
+    <t>SAHAS</t>
+  </si>
+  <si>
+    <t>34,613,437.0</t>
+  </si>
+  <si>
+    <t>RADHI</t>
+  </si>
+  <si>
+    <t>6,093,329.0</t>
+  </si>
+  <si>
+    <t>5,942,789.2</t>
+  </si>
+  <si>
+    <t>4,379,293.3</t>
+  </si>
+  <si>
+    <t>15,780,205.6</t>
+  </si>
+  <si>
+    <t>9,374,154.8</t>
+  </si>
+  <si>
+    <t>7,186,442.0</t>
+  </si>
+  <si>
+    <t>CZBIL</t>
+  </si>
+  <si>
+    <t>6,062,403.9</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>5,908,566.1</t>
+  </si>
+  <si>
+    <t>14,688,823.9</t>
+  </si>
+  <si>
+    <t>13,314,223.4</t>
   </si>
   <si>
     <t>NFS</t>
   </si>
   <si>
-    <t>42,314,326.0</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>21,725,985.0</t>
-  </si>
-  <si>
-    <t>MKCL</t>
-  </si>
-  <si>
-    <t>13,917,928.0</t>
-  </si>
-  <si>
-    <t>KBSH</t>
-  </si>
-  <si>
-    <t>11,628,135.0</t>
-  </si>
-  <si>
-    <t>GBBL</t>
-  </si>
-  <si>
-    <t>10,833,679.0</t>
-  </si>
-  <si>
-    <t>PROFL</t>
-  </si>
-  <si>
-    <t>10,499,704.4</t>
-  </si>
-  <si>
-    <t>9,778,775.9</t>
-  </si>
-  <si>
-    <t>19,149,448.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>14,732,108.2</t>
-  </si>
-  <si>
-    <t>12,200,484.6</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>7,684,404.1</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>6,779,699.6</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>55,926,119.7</t>
-  </si>
-  <si>
-    <t>SSHL</t>
-  </si>
-  <si>
-    <t>15,657,441.0</t>
-  </si>
-  <si>
-    <t>13,291,957.5</t>
-  </si>
-  <si>
-    <t>12,776,205.7</t>
-  </si>
-  <si>
-    <t>SWBBL</t>
-  </si>
-  <si>
-    <t>9,898,077.5</t>
-  </si>
-  <si>
-    <t>STC</t>
-  </si>
-  <si>
-    <t>18,199,785.0</t>
-  </si>
-  <si>
-    <t>10,512,348.0</t>
-  </si>
-  <si>
-    <t>NBL</t>
-  </si>
-  <si>
-    <t>9,106,164.4</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>5,729,483.1</t>
-  </si>
-  <si>
-    <t>CZBIL</t>
-  </si>
-  <si>
-    <t>5,238,693.9</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>38,083,043.79</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>12,381,248.0</t>
-  </si>
-  <si>
-    <t>12,168,809.6</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>9,531,075.9</t>
-  </si>
-  <si>
-    <t>HIDCLP</t>
-  </si>
-  <si>
-    <t>7,393,587.8</t>
-  </si>
-  <si>
-    <t>29,767,677.2</t>
-  </si>
-  <si>
-    <t>26,468,674.0</t>
-  </si>
-  <si>
-    <t>18,460,194.0</t>
+    <t>5,692,277.5</t>
   </si>
   <si>
     <t>NIMB</t>
   </si>
   <si>
-    <t>12,284,508.9</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>7,881,500.0</t>
+    <t>5,604,686.1</t>
+  </si>
+  <si>
+    <t>5,269,626.5</t>
   </si>
   <si>
     <t>Sell Amount</t>
   </si>
   <si>
-    <t>BNHC</t>
-  </si>
-  <si>
-    <t>18,754,142.0</t>
+    <t>27,264,910.8</t>
+  </si>
+  <si>
+    <t>17,045,740.8</t>
   </si>
   <si>
     <t>PCBLP</t>
@@ -374,145 +362,112 @@
     <t>16,375,867.2</t>
   </si>
   <si>
-    <t>15,728,397.0</t>
-  </si>
-  <si>
-    <t>JSLBB</t>
-  </si>
-  <si>
-    <t>14,246,960.0</t>
-  </si>
-  <si>
-    <t>12,799,830.3</t>
-  </si>
-  <si>
-    <t>28,075,430.6</t>
-  </si>
-  <si>
-    <t>19,921,593.2</t>
-  </si>
-  <si>
-    <t>RNLI</t>
-  </si>
-  <si>
-    <t>10,141,398.4</t>
-  </si>
-  <si>
-    <t>BPCL</t>
-  </si>
-  <si>
-    <t>10,090,905.19</t>
-  </si>
-  <si>
-    <t>MBL</t>
-  </si>
-  <si>
-    <t>9,968,916.6</t>
-  </si>
-  <si>
-    <t>34,362,598.79</t>
-  </si>
-  <si>
-    <t>10,540,059.0</t>
-  </si>
-  <si>
-    <t>AKJCL</t>
-  </si>
-  <si>
-    <t>9,717,592.5</t>
-  </si>
-  <si>
-    <t>6,969,995.1</t>
-  </si>
-  <si>
-    <t>SLBBL</t>
-  </si>
-  <si>
-    <t>6,617,494.8</t>
-  </si>
-  <si>
-    <t>17,676,097.89</t>
-  </si>
-  <si>
-    <t>13,074,815.8</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>9,351,444.4</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>8,230,664.1</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>7,274,492.7</t>
-  </si>
-  <si>
-    <t>253,368,952.8</t>
-  </si>
-  <si>
-    <t>31,673,190.0</t>
-  </si>
-  <si>
-    <t>10,327,992.5</t>
-  </si>
-  <si>
-    <t>UMRH</t>
-  </si>
-  <si>
-    <t>8,711,745.0</t>
-  </si>
-  <si>
-    <t>5,832,162.0</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>15,942,355.0</t>
-  </si>
-  <si>
-    <t>14,997,449.0</t>
-  </si>
-  <si>
-    <t>11,511,192.0</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>11,371,466.4</t>
-  </si>
-  <si>
-    <t>9,530,982.1</t>
-  </si>
-  <si>
-    <t>49,913,031.9</t>
-  </si>
-  <si>
-    <t>HBL</t>
-  </si>
-  <si>
-    <t>18,642,744.3</t>
-  </si>
-  <si>
-    <t>17,342,490.8</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>11,849,967.4</t>
-  </si>
-  <si>
-    <t>10,729,741.5</t>
+    <t>11,698,425.3</t>
+  </si>
+  <si>
+    <t>11,665,653.7</t>
+  </si>
+  <si>
+    <t>39,427,012.29</t>
+  </si>
+  <si>
+    <t>11,402,054.0</t>
+  </si>
+  <si>
+    <t>8,401,203.69</t>
+  </si>
+  <si>
+    <t>ICFC</t>
+  </si>
+  <si>
+    <t>7,019,026.2</t>
+  </si>
+  <si>
+    <t>7,017,912.0</t>
+  </si>
+  <si>
+    <t>18,725,465.2</t>
+  </si>
+  <si>
+    <t>SARBTM</t>
+  </si>
+  <si>
+    <t>18,080,159.0</t>
+  </si>
+  <si>
+    <t>14,673,430.6</t>
+  </si>
+  <si>
+    <t>9,994,215.5</t>
+  </si>
+  <si>
+    <t>MPFL</t>
+  </si>
+  <si>
+    <t>9,162,691.1</t>
+  </si>
+  <si>
+    <t>18,040,019.89</t>
+  </si>
+  <si>
+    <t>16,129,406.3</t>
+  </si>
+  <si>
+    <t>11,049,812.5</t>
+  </si>
+  <si>
+    <t>10,856,147.4</t>
+  </si>
+  <si>
+    <t>10,747,231.8</t>
+  </si>
+  <si>
+    <t>75,062,180.0</t>
+  </si>
+  <si>
+    <t>37,341,780.0</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>10,637,147.3</t>
+  </si>
+  <si>
+    <t>7,685,573.4</t>
+  </si>
+  <si>
+    <t>5,906,846.0</t>
+  </si>
+  <si>
+    <t>15,078,766.5</t>
+  </si>
+  <si>
+    <t>10,778,135.0</t>
+  </si>
+  <si>
+    <t>7,936,316.3</t>
+  </si>
+  <si>
+    <t>7,347,986.9</t>
+  </si>
+  <si>
+    <t>7,226,257.1</t>
+  </si>
+  <si>
+    <t>14,387,993.3</t>
+  </si>
+  <si>
+    <t>9,829,090.4</t>
+  </si>
+  <si>
+    <t>8,964,147.69</t>
+  </si>
+  <si>
+    <t>8,256,844.7</t>
+  </si>
+  <si>
+    <t>7,366,258.4</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -530,112 +485,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>493,007,434.7</t>
-  </si>
-  <si>
-    <t>355,207,452.2</t>
-  </si>
-  <si>
-    <t>258,643,498.5</t>
-  </si>
-  <si>
-    <t>199,605,568.3</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>195,857,320.2</t>
+    <t>450,701,630.8</t>
+  </si>
+  <si>
+    <t>378,769,816.4</t>
+  </si>
+  <si>
+    <t>260,589,466.2</t>
+  </si>
+  <si>
+    <t>232,607,699.8</t>
+  </si>
+  <si>
+    <t>212,304,698.9</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>2,158,836,124.89</t>
+    <t>2,205,445,803.44</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>1,784,478,056.51</t>
+    <t>1,907,111,368.31</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,248,376,769.0</t>
+    <t>1,229,471,229.09</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>826,042,993.33</t>
+    <t>887,553,258.43</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>413,366,445.4</t>
+    <t>355,455,885.4</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>322,979,009.6</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>317,543,057.0</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>304,578,802.14</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>296,022,085.7</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>295,306,957.2</t>
+    <t>292,218,943.14</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>208,978,382.6</t>
+    <t>223,473,489.9</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>196,117,898.7</t>
+    <t>174,083,572.6</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>104,360,047.4</t>
+    <t>118,019,488.5</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>98,190,210.2</t>
+    <t>79,597,228.5</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>39,433,984.1</t>
+    <t>40,108,409.1</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>20,673,647.85</t>
+    <t>23,611,128.09</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>3,059,356.0</t>
+    <t>3,590,701.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -647,208 +599,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>178,560,167.4</t>
-  </si>
-  <si>
-    <t>175,521,134.5</t>
-  </si>
-  <si>
-    <t>143,382,027.9</t>
-  </si>
-  <si>
-    <t>43,033,048.3</t>
-  </si>
-  <si>
-    <t>30,710,075.2</t>
-  </si>
-  <si>
-    <t>81,503,183.5</t>
-  </si>
-  <si>
-    <t>63,820,740.3</t>
-  </si>
-  <si>
-    <t>38,258,298.29</t>
-  </si>
-  <si>
-    <t>23,583,312.2</t>
-  </si>
-  <si>
-    <t>15,821,814.0</t>
-  </si>
-  <si>
-    <t>84,077,741.59</t>
-  </si>
-  <si>
-    <t>45,453,010.9</t>
-  </si>
-  <si>
-    <t>43,424,732.1</t>
-  </si>
-  <si>
-    <t>34,414,149.79</t>
-  </si>
-  <si>
-    <t>12,580,037.7</t>
-  </si>
-  <si>
-    <t>67,009,604.2</t>
-  </si>
-  <si>
-    <t>59,705,821.7</t>
-  </si>
-  <si>
-    <t>48,225,850.7</t>
-  </si>
-  <si>
-    <t>40,147,968.6</t>
-  </si>
-  <si>
-    <t>16,412,411.1</t>
-  </si>
-  <si>
-    <t>32,101,732.34</t>
-  </si>
-  <si>
-    <t>25,581,352.8</t>
-  </si>
-  <si>
-    <t>19,748,792.8</t>
-  </si>
-  <si>
-    <t>11,081,288.0</t>
-  </si>
-  <si>
-    <t>91,729,949.1</t>
-  </si>
-  <si>
-    <t>57,566,028.8</t>
-  </si>
-  <si>
-    <t>42,144,114.0</t>
-  </si>
-  <si>
-    <t>24,531,160.1</t>
-  </si>
-  <si>
-    <t>11,756,085.5</t>
-  </si>
-  <si>
-    <t>57,634,201.7</t>
-  </si>
-  <si>
-    <t>51,300,753.1</t>
-  </si>
-  <si>
-    <t>42,166,409.1</t>
-  </si>
-  <si>
-    <t>26,435,400.5</t>
-  </si>
-  <si>
-    <t>11,960,986.0</t>
-  </si>
-  <si>
-    <t>107,992,355.6</t>
-  </si>
-  <si>
-    <t>100,323,406.3</t>
-  </si>
-  <si>
-    <t>36,348,688.0</t>
-  </si>
-  <si>
-    <t>31,552,975.5</t>
-  </si>
-  <si>
-    <t>26,643,802.32</t>
-  </si>
-  <si>
-    <t>124,423,409.8</t>
-  </si>
-  <si>
-    <t>69,610,624.3</t>
-  </si>
-  <si>
-    <t>43,481,993.9</t>
-  </si>
-  <si>
-    <t>27,923,237.37</t>
-  </si>
-  <si>
-    <t>11,262,697.3</t>
-  </si>
-  <si>
-    <t>95,930,480.3</t>
-  </si>
-  <si>
-    <t>69,430,739.4</t>
-  </si>
-  <si>
-    <t>24,958,604.2</t>
-  </si>
-  <si>
-    <t>24,362,600.7</t>
-  </si>
-  <si>
-    <t>21,970,351.1</t>
-  </si>
-  <si>
-    <t>84,177,434.4</t>
-  </si>
-  <si>
-    <t>60,277,844.3</t>
-  </si>
-  <si>
-    <t>38,749,671.29</t>
-  </si>
-  <si>
-    <t>34,405,059.22</t>
-  </si>
-  <si>
-    <t>11,520,501.0</t>
-  </si>
-  <si>
-    <t>268,970,966.3</t>
-  </si>
-  <si>
-    <t>36,124,706.1</t>
-  </si>
-  <si>
-    <t>29,979,062.2</t>
-  </si>
-  <si>
-    <t>9,342,797.19</t>
-  </si>
-  <si>
-    <t>55,824,718.6</t>
-  </si>
-  <si>
-    <t>53,392,812.4</t>
-  </si>
-  <si>
-    <t>48,666,460.0</t>
-  </si>
-  <si>
-    <t>35,217,746.0</t>
-  </si>
-  <si>
-    <t>28,575,852.3</t>
-  </si>
-  <si>
-    <t>97,802,119.9</t>
-  </si>
-  <si>
-    <t>57,583,122.8</t>
-  </si>
-  <si>
-    <t>32,989,962.2</t>
-  </si>
-  <si>
-    <t>16,781,328.39</t>
-  </si>
-  <si>
-    <t>16,759,494.0</t>
+    <t>179,494,921.5</t>
+  </si>
+  <si>
+    <t>141,656,422.19</t>
+  </si>
+  <si>
+    <t>51,116,453.9</t>
+  </si>
+  <si>
+    <t>49,920,739.1</t>
+  </si>
+  <si>
+    <t>23,474,836.8</t>
+  </si>
+  <si>
+    <t>96,210,164.7</t>
+  </si>
+  <si>
+    <t>59,968,978.7</t>
+  </si>
+  <si>
+    <t>49,357,057.7</t>
+  </si>
+  <si>
+    <t>46,671,561.0</t>
+  </si>
+  <si>
+    <t>14,004,817.6</t>
+  </si>
+  <si>
+    <t>85,411,188.16</t>
+  </si>
+  <si>
+    <t>61,337,778.6</t>
+  </si>
+  <si>
+    <t>50,935,996.7</t>
+  </si>
+  <si>
+    <t>21,763,270.5</t>
+  </si>
+  <si>
+    <t>19,612,941.5</t>
+  </si>
+  <si>
+    <t>58,759,576.3</t>
+  </si>
+  <si>
+    <t>57,120,033.5</t>
+  </si>
+  <si>
+    <t>49,134,959.1</t>
+  </si>
+  <si>
+    <t>29,278,405.2</t>
+  </si>
+  <si>
+    <t>19,810,435.3</t>
+  </si>
+  <si>
+    <t>177,316,329.2</t>
+  </si>
+  <si>
+    <t>61,664,434.5</t>
+  </si>
+  <si>
+    <t>28,223,705.6</t>
+  </si>
+  <si>
+    <t>13,636,031.8</t>
+  </si>
+  <si>
+    <t>8,594,253.1</t>
+  </si>
+  <si>
+    <t>60,429,569.5</t>
+  </si>
+  <si>
+    <t>59,474,288.2</t>
+  </si>
+  <si>
+    <t>51,466,182.6</t>
+  </si>
+  <si>
+    <t>23,789,762.8</t>
+  </si>
+  <si>
+    <t>14,183,719.5</t>
+  </si>
+  <si>
+    <t>51,819,322.2</t>
+  </si>
+  <si>
+    <t>37,360,629.5</t>
+  </si>
+  <si>
+    <t>33,501,569.4</t>
+  </si>
+  <si>
+    <t>24,442,531.0</t>
+  </si>
+  <si>
+    <t>7,354,071.4</t>
+  </si>
+  <si>
+    <t>129,762,315.0</t>
+  </si>
+  <si>
+    <t>91,100,497.6</t>
+  </si>
+  <si>
+    <t>47,672,577.0</t>
+  </si>
+  <si>
+    <t>37,573,980.5</t>
+  </si>
+  <si>
+    <t>15,610,975.32</t>
+  </si>
+  <si>
+    <t>115,904,661.7</t>
+  </si>
+  <si>
+    <t>74,739,685.4</t>
+  </si>
+  <si>
+    <t>30,750,281.2</t>
+  </si>
+  <si>
+    <t>29,184,508.5</t>
+  </si>
+  <si>
+    <t>14,433,229.7</t>
+  </si>
+  <si>
+    <t>122,203,305.8</t>
+  </si>
+  <si>
+    <t>69,192,940.9</t>
+  </si>
+  <si>
+    <t>38,775,552.79</t>
+  </si>
+  <si>
+    <t>32,772,813.07</t>
+  </si>
+  <si>
+    <t>13,803,205.3</t>
+  </si>
+  <si>
+    <t>99,494,958.7</t>
+  </si>
+  <si>
+    <t>78,733,514.0</t>
+  </si>
+  <si>
+    <t>44,285,515.13</t>
+  </si>
+  <si>
+    <t>40,605,929.29</t>
+  </si>
+  <si>
+    <t>14,082,447.8</t>
+  </si>
+  <si>
+    <t>84,688,656.39</t>
+  </si>
+  <si>
+    <t>66,236,107.0</t>
+  </si>
+  <si>
+    <t>29,019,616.5</t>
+  </si>
+  <si>
+    <t>12,914,225.3</t>
+  </si>
+  <si>
+    <t>12,117,205.5</t>
+  </si>
+  <si>
+    <t>70,145,581.59</t>
+  </si>
+  <si>
+    <t>69,388,443.2</t>
+  </si>
+  <si>
+    <t>48,565,933.3</t>
+  </si>
+  <si>
+    <t>36,203,200.7</t>
+  </si>
+  <si>
+    <t>11,357,505.6</t>
+  </si>
+  <si>
+    <t>81,000,810.09</t>
+  </si>
+  <si>
+    <t>74,926,465.0</t>
+  </si>
+  <si>
+    <t>35,902,631.6</t>
+  </si>
+  <si>
+    <t>20,695,291.0</t>
+  </si>
+  <si>
+    <t>12,499,806.5</t>
   </si>
 </sst>
 </file>
@@ -1657,61 +1615,61 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.09693193505636945</v>
+        <v>0.1177640300114029</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="12">
-        <v>0.02437727437847149</v>
+        <v>0.03934320501389042</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.03462046687453274</v>
+        <v>0.02318771105878962</v>
       </c>
       <c r="K9" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>82</v>
-      </c>
       <c r="M9" s="16">
-        <v>0.1019442068335147</v>
+        <v>0.03913283112464924</v>
       </c>
       <c r="N9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>90</v>
-      </c>
       <c r="P9" s="18">
-        <v>0.03449212702832401</v>
+        <v>0.3222913932160359</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="S9" s="16">
-        <v>0.07390376884095466</v>
+        <v>0.02992478261156574</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="V9" s="18">
-        <v>0.06494379021878459</v>
+        <v>0.03114967426952197</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1723,61 +1681,61 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.07787702119433738</v>
+        <v>0.04892929398268532</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.02036669807495107</v>
+        <v>0.02711869888648014</v>
       </c>
       <c r="H10" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="J10" s="14">
-        <v>0.02663431676621343</v>
+        <v>0.02245670442111016</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02854096462171597</v>
+        <v>0.02230079140473571</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="O10" s="17" t="s">
         <v>91</v>
       </c>
       <c r="P10" s="18">
-        <v>0.01992294098979454</v>
+        <v>0.06350409882933661</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="S10" s="16">
-        <v>0.02402698941187396</v>
+        <v>0.01777667234938723</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>56</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="V10" s="18">
-        <v>0.05774639385116007</v>
+        <v>0.02823464457638759</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1789,34 +1747,34 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.07703576487368123</v>
+        <v>0.02121401876283937</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G11" s="12">
-        <v>0.01897520705030839</v>
+        <v>0.0242564344188866</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>76</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02205737068491723</v>
+        <v>0.0184131859655548</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M11" s="16">
-        <v>0.02422907349680272</v>
+        <v>0.02163074008622417</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>92</v>
@@ -1825,25 +1783,25 @@
         <v>93</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01725794998268396</v>
+        <v>0.01117922403994908</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>56</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02361473249015852</v>
+        <v>0.01362800460601259</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="V11" s="18">
-        <v>0.04027438750021335</v>
+        <v>0.01207125847405175</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1855,61 +1813,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.04238038200568697</v>
+        <v>0.0209035284586298</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01839024997482703</v>
+        <v>0.01360522451137771</v>
       </c>
       <c r="H12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>78</v>
-      </c>
       <c r="J12" s="14">
-        <v>0.01389270633777922</v>
+        <v>0.01544762685282592</v>
       </c>
       <c r="K12" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0.009580190902092046</v>
+      </c>
+      <c r="N12" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="L12" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12" s="16">
-        <v>0.02328894197228435</v>
-      </c>
-      <c r="N12" s="17" t="s">
+      <c r="O12" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="O12" s="17" t="s">
-        <v>95</v>
-      </c>
       <c r="P12" s="18">
-        <v>0.01085848315745684</v>
+        <v>0.01090303377496763</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01849595935184135</v>
+        <v>0.01149643568718828</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02680096816362925</v>
+        <v>0.0118855088458047</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1921,61 +1879,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02175990097892201</v>
+        <v>0.01867767553572381</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01712754249051184</v>
+        <v>0.01353526715670261</v>
       </c>
       <c r="H13" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="J13" s="14">
+        <v>0.0148878331077559</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="M13" s="16">
+        <v>0.009202372582909537</v>
+      </c>
+      <c r="N13" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="J13" s="14">
-        <v>0.01225708257601383</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="16">
-        <v>0.01804258306006089</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>96</v>
-      </c>
       <c r="O13" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P13" s="18">
-        <v>0.009928342310708951</v>
+        <v>0.008034540878614615</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01434796038221353</v>
+        <v>0.01120470547535621</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01719497558275561</v>
+        <v>0.01117496881401384</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1986,7 +1944,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1995,7 +1953,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2004,7 +1962,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2013,7 +1971,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2022,7 +1980,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2031,7 +1989,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2040,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2049,566 +2007,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D16" s="10">
-        <v>0.01878341869722558</v>
+        <v>0.03020293644920594</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="F16" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.0613569462500281</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="12">
-        <v>0.04917416407312456</v>
-      </c>
-      <c r="H16" s="13" t="s">
+      <c r="J16" s="14">
+        <v>0.03112833489182814</v>
+      </c>
+      <c r="K16" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="J16" s="14">
-        <v>0.06212446507482923</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>105</v>
-      </c>
       <c r="L16" s="15" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="M16" s="16">
-        <v>0.03222064734677192</v>
+        <v>0.0300774723627883</v>
       </c>
       <c r="N16" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.1377140356522657</v>
+      </c>
+      <c r="Q16" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="O16" s="17" t="s">
+      <c r="R16" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="S16" s="16">
+        <v>0.02859460903114342</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="U16" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="P16" s="18">
-        <v>0.4801833705733903</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="S16" s="16">
-        <v>0.0309376562673921</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>159</v>
-      </c>
       <c r="V16" s="18">
-        <v>0.1088946729406587</v>
+        <v>0.03051172154681931</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D17" s="10">
-        <v>0.0164014312223808</v>
+        <v>0.01888256410917863</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>58</v>
       </c>
       <c r="F17" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.0177440585427752</v>
+      </c>
+      <c r="H17" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="G17" s="12">
-        <v>0.0348927041074427</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>105</v>
-      </c>
       <c r="I17" s="13" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="J17" s="14">
-        <v>0.01905547164937186</v>
+        <v>0.03005560813781548</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M17" s="16">
-        <v>0.02383325954626002</v>
+        <v>0.02689197544712429</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O17" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.06850969719023699</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="R17" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="S17" s="16">
+        <v>0.02043910928721411</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="P17" s="18">
-        <v>0.06002684607934883</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="S17" s="16">
-        <v>0.02910397629771407</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="U17" s="17" t="s">
-        <v>161</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.04067265533642787</v>
+        <v>0.02084394001930171</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.01814050594077997</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.01307408737781628</v>
+      </c>
+      <c r="H18" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0.01575295027024892</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="F18" s="11" t="s">
+      <c r="I18" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="G18" s="12">
-        <v>0.01776267641118648</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>134</v>
-      </c>
       <c r="J18" s="14">
-        <v>0.01756852674011584</v>
+        <v>0.02439242266348602</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="M18" s="16">
-        <v>0.01704615995566222</v>
+        <v>0.01842295252028756</v>
       </c>
       <c r="N18" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="O18" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.01951561335562866</v>
+      </c>
+      <c r="Q18" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O18" s="17" t="s">
+      <c r="R18" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="S18" s="16">
+        <v>0.015050028246408</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="U18" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="P18" s="18">
-        <v>0.01957355151489854</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="R18" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.02233856298670766</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>162</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.03783590761278484</v>
+        <v>0.01900970988963143</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.01295902995918413</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="F19" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="10">
-        <v>0.01426920063005948</v>
-      </c>
-      <c r="E19" s="11" t="s">
+      <c r="G19" s="12">
+        <v>0.01092312067685989</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.01767423748617931</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="J19" s="14">
-        <v>0.01260111959755736</v>
+        <v>0.01661391499449101</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01500316002412704</v>
+        <v>0.01810006170724103</v>
       </c>
       <c r="N19" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="O19" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0.01410046083414717</v>
+      </c>
+      <c r="Q19" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="R19" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="S19" s="16">
+        <v>0.01393435017190985</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="U19" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="O19" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="P19" s="18">
-        <v>0.01651044862224287</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="R19" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="S19" s="16">
-        <v>0.02206741216961977</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>164</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.02585293409876926</v>
+        <v>0.01750977645657723</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.01292272694101549</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D20" s="10">
-        <v>0.01281981184627558</v>
-      </c>
-      <c r="E20" s="11" t="s">
+      <c r="G20" s="12">
+        <v>0.01092138674102443</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.01746057424742383</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>137</v>
-      </c>
       <c r="J20" s="14">
-        <v>0.01196383099480427</v>
+        <v>0.01523162784074241</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="L20" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.01791847066870362</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.01083709000506571</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="R20" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="M20" s="16">
-        <v>0.01326021530540215</v>
-      </c>
-      <c r="N20" s="17" t="s">
+      <c r="S20" s="16">
+        <v>0.01370350794496514</v>
+      </c>
+      <c r="T20" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="O20" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.01105307961350995</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.01849577732401938</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>105</v>
-      </c>
       <c r="U20" s="17" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02340895046650758</v>
+        <v>0.01562116554104308</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>175</v>
+        <v>54</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2639079254311167</v>
+        <v>0.2696057472490685</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2181443493747822</v>
+        <v>0.2331357155710165</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D33" s="22">
-        <v>0.152608398323878</v>
+        <v>0.1502972818122352</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1009800096326153</v>
+        <v>0.1084993605773685</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="D35" s="22">
-        <v>0.05053217323473662</v>
+        <v>0.04345286991293727</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D36" s="22">
-        <v>0.03723337722410849</v>
+        <v>0.03948271913676442</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D37" s="22">
-        <v>0.03618735744606823</v>
+        <v>0.03881819858475587</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="D38" s="22">
-        <v>0.03609993623022154</v>
+        <v>0.03572244051626675</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02554665950604579</v>
+        <v>0.02731862063470226</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02397452367463236</v>
+        <v>0.02128092723983118</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01275754249694628</v>
+        <v>0.01442734722259826</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01200330788092942</v>
+        <v>0.009730400191710661</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D43" s="22">
-        <v>0.004820625713702522</v>
+        <v>0.004903071111274303</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="D44" s="22">
-        <v>0.002527259689739056</v>
+        <v>0.002886353326905609</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0003739923960909162</v>
+        <v>0.0004389469125646211</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2987,331 +2945,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1788389139274347</v>
+        <v>0.1988370234103135</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1427529634366847</v>
+        <v>0.149723794927374</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1520049386252974</v>
+        <v>0.1419835523527301</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1221475937726599</v>
+        <v>0.09796771522477093</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="P9" s="18">
-        <v>0.06083901703786813</v>
+        <v>0.325316254885985</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1780106913113635</v>
+        <v>0.11459557476222</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1257398580172698</v>
+        <v>0.1098900101455644</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1757951368569964</v>
+        <v>0.1569211045182838</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1117821343328025</v>
+        <v>0.09332468244785012</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="J10" s="14">
-        <v>0.08217492526213944</v>
+        <v>0.1019650456417825</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1088339879326501</v>
+        <v>0.0952341648446736</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="P10" s="18">
-        <v>0.0484816315321292</v>
+        <v>0.1131336464143435</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1117123543976529</v>
+        <v>0.1127840276911607</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1119222479136553</v>
+        <v>0.07922836078314571</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D11" s="10">
-        <v>0.1436058585726278</v>
+        <v>0.0566246858453124</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="G11" s="12">
-        <v>0.06700947403324038</v>
+        <v>0.07681024149928896</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="J11" s="14">
-        <v>0.07850798097174962</v>
+        <v>0.08467361138385246</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="M11" s="16">
-        <v>0.0879078706846704</v>
+        <v>0.08192093925445081</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="P11" s="18">
-        <v>0.03742779763132644</v>
+        <v>0.0517810753596212</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="S11" s="16">
-        <v>0.08178466184110109</v>
+        <v>0.09759786185245566</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="V11" s="18">
-        <v>0.09199395735418178</v>
+        <v>0.07104469230703928</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="D12" s="10">
-        <v>0.04310022628797581</v>
+        <v>0.0553001226226161</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="G12" s="12">
-        <v>0.04130621111508509</v>
+        <v>0.07263102864332198</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="J12" s="14">
-        <v>0.06221766461185239</v>
+        <v>0.03617823991178836</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="M12" s="16">
-        <v>0.07318320736104729</v>
+        <v>0.0488148254886081</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>90</v>
+        <v>217</v>
       </c>
       <c r="P12" s="18">
-        <v>0.03449212702832401</v>
+        <v>0.02501756503022733</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04760504950580789</v>
+        <v>0.04511370119098533</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="V12" s="18">
-        <v>0.05767380144869191</v>
+        <v>0.05183375361812957</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="D13" s="10">
-        <v>0.0307580160534608</v>
+        <v>0.02600444979361095</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02771193392027473</v>
+        <v>0.02179452082714996</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02274356829884721</v>
+        <v>0.03260363385929842</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02991715214268784</v>
+        <v>0.03302922189296232</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02100119277966429</v>
+        <v>0.01576758465871888</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="S13" s="16">
-        <v>0.0228138021170067</v>
+        <v>0.02689728723565717</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02609514206885512</v>
+        <v>0.01559532132894638</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3322,7 +3280,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3331,7 +3289,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3340,7 +3298,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3349,7 +3307,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3358,7 +3316,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3367,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3376,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3385,331 +3343,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.1437453062728099</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.1803726857095533</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0.203145042710655</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="L16" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="D16" s="10">
-        <v>0.1081609401984091</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="F16" s="11" t="s">
+      <c r="M16" s="16">
+        <v>0.1658843442038561</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="O16" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="G16" s="12">
-        <v>0.2179278122289179</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="I16" s="13" t="s">
+      <c r="P16" s="18">
+        <v>0.1553754053880673</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="R16" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="J16" s="14">
-        <v>0.1734336162318708</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="L16" s="15" t="s">
+      <c r="S16" s="16">
+        <v>0.1330205279798031</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="U16" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="M16" s="16">
-        <v>0.1534417518901854</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0.5097522161141275</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="S16" s="16">
-        <v>0.1083331763262511</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>273</v>
-      </c>
       <c r="V16" s="18">
-        <v>0.2133737313483773</v>
+        <v>0.1717733745982485</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.100917349764586</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.1163110921248225</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.1150230989447286</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="L17" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="D17" s="10">
-        <v>0.1004800190627104</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="F17" s="11" t="s">
+      <c r="M17" s="16">
+        <v>0.1312695387525712</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="O17" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="G17" s="12">
-        <v>0.1219231259292184</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="I17" s="13" t="s">
+      <c r="P17" s="18">
+        <v>0.1215211388859914</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="R17" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="J17" s="14">
-        <v>0.1255244857957271</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="L17" s="15" t="s">
+      <c r="S17" s="16">
+        <v>0.131584729068104</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="M17" s="16">
-        <v>0.1098766919600466</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="O17" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="P17" s="18">
-        <v>0.06846333358674683</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="S17" s="16">
-        <v>0.10361383102939</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="U17" s="17" t="s">
-        <v>274</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.1256284197836475</v>
+        <v>0.1588918891536809</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.05280970196685465</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.04785407873174427</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.06445865992019062</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="L18" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="D18" s="10">
-        <v>0.03640543117348791</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F18" s="11" t="s">
+      <c r="M18" s="16">
+        <v>0.07383563681071208</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="O18" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="G18" s="12">
-        <v>0.07615878569161469</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="I18" s="13" t="s">
+      <c r="P18" s="18">
+        <v>0.05324130609177722</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="R18" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="J18" s="14">
-        <v>0.04512289492316822</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="L18" s="15" t="s">
+      <c r="S18" s="16">
+        <v>0.09209797598139667</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="U18" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="M18" s="16">
-        <v>0.07063433914114206</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="P18" s="18">
-        <v>0.06002684607934883</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="R18" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.0944418946404585</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>275</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.07197381139440846</v>
+        <v>0.07613647541643184</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.04162289594526028</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.04541739824825602</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.05447998699601024</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="L19" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="D19" s="10">
-        <v>0.03160223218741761</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="F19" s="11" t="s">
+      <c r="M19" s="16">
+        <v>0.06770079650999086</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="O19" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="G19" s="12">
-        <v>0.04890759737395384</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="I19" s="13" t="s">
+      <c r="P19" s="18">
+        <v>0.023693291127244</v>
+      </c>
+      <c r="Q19" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="R19" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J19" s="14">
-        <v>0.04404537459836013</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="L19" s="15" t="s">
+      <c r="S19" s="16">
+        <v>0.06865391606750577</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="U19" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="M19" s="16">
-        <v>0.06271481899829431</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="O19" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="P19" s="18">
-        <v>0.05681614489360322</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="R19" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="S19" s="16">
-        <v>0.06834338592135998</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>276</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.03661162622396791</v>
+        <v>0.04388721506580044</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.01729319046589664</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.02246122257955644</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.0229458009491298</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="L20" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="D20" s="10">
-        <v>0.02668539540026252</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F20" s="11" t="s">
+      <c r="M20" s="16">
+        <v>0.02347915561362042</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="O20" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="G20" s="12">
-        <v>0.01972663332672579</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="I20" s="13" t="s">
+      <c r="P20" s="18">
+        <v>0.02223102593387016</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="R20" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="J20" s="14">
-        <v>0.03972040408054604</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="L20" s="15" t="s">
+      <c r="S20" s="16">
+        <v>0.02153779834716732</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="M20" s="16">
-        <v>0.02099999683635681</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.01770641509348983</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.05545415943912715</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>277</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.03656399037103839</v>
+        <v>0.02650756136487234</v>
       </c>
     </row>
   </sheetData>
